--- a/artfynd/A 44448-2025 artfynd.xlsx
+++ b/artfynd/A 44448-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>87748255</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526272.294226967</v>
+        <v>526272</v>
       </c>
       <c r="R2" t="n">
-        <v>6909036.762618866</v>
+        <v>6909037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-07-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87747842</v>
+        <v>87748250</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Riberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526300.1743366907</v>
+        <v>526322</v>
       </c>
       <c r="R3" t="n">
-        <v>6908985.361632757</v>
+        <v>6909053</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +840,9 @@
           <t>2020-07-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-07-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,50 +869,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87748250</v>
+        <v>87747842</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Riberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526322.4641121804</v>
+        <v>526300</v>
       </c>
       <c r="R4" t="n">
-        <v>6909052.967163033</v>
+        <v>6908985</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,19 +942,9 @@
           <t>2020-07-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-07-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87748077</v>
+        <v>87747840</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,34 +982,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Riberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>526269.9803704005</v>
+        <v>526365</v>
       </c>
       <c r="R5" t="n">
-        <v>6909034.884349083</v>
+        <v>6908938</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,24 +1044,9 @@
           <t>2020-07-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-07-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fåtalig</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,52 +1073,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126379643</v>
+        <v>87747844</v>
       </c>
       <c r="B6" t="n">
-        <v>78739</v>
+        <v>57144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nylandet, Hls</t>
+          <t>Riberget, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>526251</v>
+        <v>526387</v>
       </c>
       <c r="R6" t="n">
-        <v>6909246</v>
+        <v>6909224</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,17 +1143,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,64 +1163,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126379642</v>
+        <v>87748077</v>
       </c>
       <c r="B7" t="n">
-        <v>78739</v>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nylandet, Hls</t>
+          <t>Riberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>526236</v>
+        <v>526270</v>
       </c>
       <c r="R7" t="n">
-        <v>6909242</v>
+        <v>6909035</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,17 +1240,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Fåtalig</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,22 +1265,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126379644</v>
+        <v>126379642</v>
       </c>
       <c r="B8" t="n">
-        <v>78739</v>
+        <v>79085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>526296</v>
+        <v>526236</v>
       </c>
       <c r="R8" t="n">
-        <v>6909268</v>
+        <v>6909242</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1448,6 +1380,218 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126379643</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nylandet, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>526251</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6909246</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126379644</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nylandet, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>526296</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6909268</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44448-2025 artfynd.xlsx
+++ b/artfynd/A 44448-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748255</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748250</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87747842</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87747840</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87747844</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748077</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379642</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,6 +1526,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379643</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,8 +1637,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379644</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>